--- a/output/full_scan/batch_seq6_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1346.259383362164</v>
+        <v>1456.259383362164</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>276.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>77.48025102584984</v>
+        <v>77.48025103203273</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46.51567856382659</v>
+        <v>46.51567874904204</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.625938336216453</v>
@@ -564,17 +564,17 @@
         <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3618859537257144</v>
+        <v>0.3618859535158414</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1235.705633140205</v>
+        <v>1250.705633140205</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>548</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>70.90637167818201</v>
+        <v>70.90637169023725</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>43.54242636070714</v>
+        <v>43.54242646274108</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.570563314020501</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.9433984938482638</v>
+        <v>-0.9433984946114506</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1111.593546502259</v>
+        <v>1126.593546502259</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>60.9</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.55577917144601</v>
+        <v>65.55577918255076</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.74837719815951</v>
+        <v>16.74837731469402</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.159354650225832</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.5278048199752132</v>
+        <v>0.5278048198934637</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1080.665038472125</v>
+        <v>1095.665038472125</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>6485</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.36309021496221</v>
+        <v>62.36309021216904</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.77943396968899</v>
+        <v>20.77943407391409</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.066503847212455</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-13.593930424137</v>
+        <v>-13.59393042928886</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.2077649615458</v>
+        <v>56.20776505436839</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.19018896541712</v>
+        <v>22.19018902543641</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.544982151357584</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1099989582785911</v>
+        <v>0.1099989581927368</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1032.736894813746</v>
+        <v>1047.736894813746</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>327.5</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.82829687436723</v>
+        <v>68.8282968958999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>51.37801120643167</v>
+        <v>51.37801134998608</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.7736894813745946</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3114068223875676</v>
+        <v>0.3114068216244163</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1029.767095862767</v>
+        <v>1044.767095862767</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>54.1</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.72745152707906</v>
+        <v>57.72745155201733</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>28.06021509031592</v>
+        <v>28.0602151536011</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.976709586276669</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.06277532278393071</v>
+        <v>0.06277532242142039</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.61073908915255</v>
+        <v>57.61073910443616</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>32.07712716815988</v>
+        <v>32.07712730206052</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.7150193145258779</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-3.442586758281651</v>
+        <v>-3.442586758682328</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6435</v>
+        <v>6449</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>919.9145675282856</v>
+        <v>953.3437493727532</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>274.5</v>
+        <v>421</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.63859251051305</v>
+        <v>71.55611808177314</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.58393755703204</v>
+        <v>51.26672431668993</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4914567528285691</v>
+        <v>0.834374937275311</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-4.256728511004564</v>
+        <v>-1.808850820453337</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6239</v>
+        <v>6435</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>895.7795535831103</v>
+        <v>919.9145675282856</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>347.5</v>
+        <v>274.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,29 +1029,29 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.49849993337824</v>
+        <v>58.63859253106008</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.83148906588974</v>
+        <v>29.58393768056126</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.077955358311032</v>
+        <v>0.4914567528285691</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-3.741836540993031</v>
+        <v>-4.256728511691414</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>892.3773218122519</v>
+        <v>907.377321812252</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>70.09999999999999</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.65163547624444</v>
+        <v>62.65163548839581</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45.32089663606213</v>
+        <v>45.32089669166185</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.237732181225198</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.129115937127799</v>
+        <v>0.1291159370419397</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6411</v>
+        <v>6241</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>890.3954863654616</v>
+        <v>905</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>97.7</v>
+        <v>13.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.46034061559367</v>
+        <v>78.48474560324163</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.09479092221769</v>
+        <v>21.25988081093717</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5395486365461576</v>
+        <v>5.987140203893656</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.309144999901543</v>
+        <v>0.3539366748509574</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6241</v>
+        <v>6409</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>890</v>
+        <v>895.0506050068968</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13.9</v>
+        <v>930</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>78.48474553007088</v>
+        <v>66.72330392239382</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>21.25988065506211</v>
+        <v>33.15280337789404</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.987140203893656</v>
+        <v>1.005060500689684</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3539366749463558</v>
+        <v>19.37109762222321</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6409</v>
+        <v>6411</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>880.0506050068968</v>
+        <v>890.3954863654616</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>930</v>
+        <v>97.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>66.72330393289612</v>
+        <v>56.46034064864305</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33.15280339879573</v>
+        <v>30.09479102091313</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.005060500689684</v>
+        <v>0.5395486365461576</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>19.37109762413122</v>
+        <v>-1.309145000206817</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>874.7670326253359</v>
+        <v>889.7670326253359</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>27.6</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.16671795729109</v>
+        <v>57.16671797508356</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41.69010544052587</v>
+        <v>41.69010544052585</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.476703262533591</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.0001580524423265</v>
+        <v>-0.0001580525663424</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6265</v>
+        <v>6239</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>861.103866678321</v>
+        <v>885.7795535831103</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>58.9</v>
+        <v>347.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,29 +1347,29 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.5455205292527</v>
+        <v>61.49849993337824</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.2059115572959</v>
+        <v>31.83148905132208</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.110386667832095</v>
+        <v>3.077955358311032</v>
       </c>
       <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.143696381378064</v>
+        <v>-3.741836541088407</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>860.493267929993</v>
+        <v>875.493267929993</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>98.59999999999999</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.28754694654706</v>
+        <v>60.28754696001538</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>44.98265994886761</v>
+        <v>44.98266013128562</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.049326792999299</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.5445922014072178</v>
+        <v>-0.5445922016457132</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>856.8464277760215</v>
+        <v>871.8464277760215</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>50.3</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.92481116354831</v>
+        <v>64.92481121502519</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>37.40687815514468</v>
+        <v>37.40687830352461</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>2.18464277760215</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0441392246112606</v>
+        <v>-0.0441392247066549</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6269</v>
+        <v>6265</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>839.5476310391889</v>
+        <v>861.103866678321</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>72.3</v>
+        <v>58.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.13211432368707</v>
+        <v>60.54552053346789</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.46660148914722</v>
+        <v>36.20591167047512</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.9547631039188856</v>
+        <v>1.110386667832095</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2895125418749802</v>
+        <v>-0.1436963814047724</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6208</v>
+        <v>6269</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>834.7890415035494</v>
+        <v>849.5476310391889</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.7353316641973</v>
+        <v>58.1321143246298</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.65564948405721</v>
+        <v>24.46660168544805</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4789041503549378</v>
+        <v>0.9547631039188856</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-2.148974601546179</v>
+        <v>0.289512541646034</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6166</v>
+        <v>6257</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>825.948262679313</v>
+        <v>837.7361398085523</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>128.5</v>
+        <v>221.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.96246168171538</v>
+        <v>55.62576057534357</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>62.54396087944585</v>
+        <v>31.99304250332395</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.594826267931301</v>
+        <v>0.7736139808552306</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-2.172082465855127</v>
+        <v>-3.22046595268163</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6257</v>
+        <v>6208</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>822.7361398085523</v>
+        <v>834.7890415035494</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>221.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,29 +1665,29 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.62576054412452</v>
+        <v>50.73533167186252</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.99304232621359</v>
+        <v>28.6556494979795</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7736139808552306</v>
+        <v>0.4789041503549378</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-3.220465952338217</v>
+        <v>-2.148974601698814</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>815.0381482831352</v>
+        <v>830.0381482831352</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>109.5</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>65.05623422126345</v>
+        <v>65.05623417548266</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46.98446713344948</v>
+        <v>46.98446711014618</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1.00381482831352</v>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6292</v>
+        <v>6166</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>814.8195756958528</v>
+        <v>825.948262679313</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>60.5</v>
+        <v>128.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.24213719957827</v>
+        <v>58.96246168436824</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.54551218899447</v>
+        <v>62.54396093482066</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4819575695852738</v>
+        <v>0.594826267931301</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,11 +1789,11 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.816898447434713</v>
+        <v>-2.172082466160395</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>805.3089943963762</v>
+        <v>820.3089943963762</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>49.1</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.23948998099718</v>
+        <v>51.23948992842966</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.32878841424126</v>
+        <v>20.32878844473996</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.5308994396376192</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0156749770276955</v>
+        <v>0.0156749770467775</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>804.6970290947646</v>
+        <v>819.6970290947646</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>34.6</v>
@@ -1880,7 +1880,7 @@
         <v>60.03543334847273</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46.63792204842198</v>
+        <v>46.63792202489997</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.469702909476467</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1781557874712954</v>
+        <v>0.1781557874617592</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6170</v>
+        <v>6292</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>794.0165667905636</v>
+        <v>814.8195756958528</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>52.3</v>
+        <v>60.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.18261941377531</v>
+        <v>56.24213719656247</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.68283861306845</v>
+        <v>33.54551235803976</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.40165667905636</v>
+        <v>0.4819575695852738</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0672824891136149</v>
+        <v>-0.8168984475491938</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6278</v>
+        <v>6446</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>793.0270916147034</v>
+        <v>795.6034589679434</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>211</v>
+        <v>949</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.34132125020263</v>
+        <v>63.62339063041533</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.63477646513477</v>
+        <v>41.38569367501354</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8027091614703419</v>
+        <v>0.5603458967943393</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-5.478724500730378</v>
+        <v>-1.08040281342091</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6214</v>
+        <v>6170</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>788.7774289253136</v>
+        <v>794.0165667905636</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>145.5</v>
+        <v>52.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>62.19885724048169</v>
+        <v>57.18261963435096</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.87577182077481</v>
+        <v>19.68283877121274</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8777428925313685</v>
+        <v>1.40165667905636</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0278474540462658</v>
+        <v>0.0672824887606441</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6419</v>
+        <v>6278</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>782.739357047826</v>
+        <v>793.0270916147034</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.64594739851017</v>
+        <v>54.3413212591142</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.25758265193596</v>
+        <v>24.63477654485832</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.773935704782608</v>
+        <v>0.8027091614703419</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.88229607086776</v>
+        <v>-5.478724501016565</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6446</v>
+        <v>6419</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>780.6034589679434</v>
+        <v>782.739357047826</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>949</v>
+        <v>145</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.62339063418753</v>
+        <v>51.64594742176576</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>41.38569369119492</v>
+        <v>18.25758271679724</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5603458967943393</v>
+        <v>1.773935704782608</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.080402811989877</v>
+        <v>-1.882296071516443</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6205</v>
+        <v>6214</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>774.9465199296814</v>
+        <v>778.7774289253136</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>86.5</v>
+        <v>145.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>55.63469252991637</v>
+        <v>62.19885727010053</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.99243122175817</v>
+        <v>27.87577182376939</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9946519929681404</v>
+        <v>0.8777428925313685</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,11 +2213,11 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.4405588735254373</v>
+        <v>-0.0278474547140668</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>760.7088368506403</v>
+        <v>775.7088368506403</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>120.5</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.80182622615808</v>
+        <v>54.80182602134659</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.79832205122325</v>
+        <v>22.79832219919779</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.5708836850640272</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.203028297241663</v>
+        <v>-0.2030282961922953</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6190</v>
+        <v>6205</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>758.768407067539</v>
+        <v>774.9465199296814</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.58565340053259</v>
+        <v>55.63469259225712</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.81272775927206</v>
+        <v>18.99243130369872</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3768407067538983</v>
+        <v>0.9946519929681404</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.102887883377423</v>
+        <v>-0.4405588740119597</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6227</v>
+        <v>6190</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>756.6228961706978</v>
+        <v>758.768407067539</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>126</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.25416494914858</v>
+        <v>52.58565344540836</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>32.75234699804825</v>
+        <v>34.81272791645069</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6622896170697827</v>
+        <v>0.3768407067538983</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.531070699380884</v>
+        <v>-1.102887883654088</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6177</v>
+        <v>6227</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>728.4465130829216</v>
+        <v>756.6228961706978</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>47.15</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>62.0917474305897</v>
+        <v>54.25416502158576</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.44163997158911</v>
+        <v>32.75234727980906</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.344651308292161</v>
+        <v>0.6622896170697827</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,11 +2425,11 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.5209264605693289</v>
+        <v>-1.53107070056382</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>724.7968873070729</v>
+        <v>749.7968873070729</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>58.1</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.24145093432279</v>
+        <v>50.24145095225879</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>33.47173767363563</v>
+        <v>33.47173794522273</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.4796887307072856</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.852370187129901</v>
+        <v>-0.8523701873683969</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6209</v>
+        <v>6177</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>721.1819027201113</v>
+        <v>743.4465130829216</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>47.15</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.83088104569909</v>
+        <v>62.09174746261546</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>33.76428582697227</v>
+        <v>19.44163992341037</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6181902720111367</v>
+        <v>1.344651308292161</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.8172204721344665</v>
+        <v>0.5209264604357762</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6414</v>
+        <v>6443</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>716.9182382508668</v>
+        <v>735.2465912330596</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>375.5</v>
+        <v>41.75</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.03049403111508</v>
+        <v>54.05286657260646</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>34.57377914928338</v>
+        <v>22.54567483849593</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.191823825086683</v>
+        <v>1.524659123305958</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.2088232948773107</v>
+        <v>-0.0881266049752005</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6443</v>
+        <v>6414</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>715.2465912330596</v>
+        <v>721.9182382508668</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>41.75</v>
+        <v>375.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.05286650160778</v>
+        <v>55.03049403863271</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.54567477803669</v>
+        <v>34.57377921341151</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.524659123305958</v>
+        <v>1.191823825086683</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0881266048607267</v>
+        <v>-0.2088232950680684</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6202</v>
+        <v>6209</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>698.1085319230616</v>
+        <v>721.1819027201113</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>59.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.6543338231995</v>
+        <v>54.83088105459414</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.46527611626376</v>
+        <v>33.76428601470448</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.310853192306162</v>
+        <v>0.6181902720111367</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.3826920296176629</v>
+        <v>-0.817220472287107</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6277</v>
+        <v>6202</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>678.9126877079127</v>
+        <v>718.1085319230616</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.29561307529147</v>
+        <v>56.65433385961344</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>42.07064275777451</v>
+        <v>16.4652761924551</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3912687707912746</v>
+        <v>2.310853192306162</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.7319183994187015</v>
+        <v>-0.3826920299515541</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6213</v>
+        <v>6270</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>671.1440412534811</v>
+        <v>682.4362449166448</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>252.5</v>
+        <v>34.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>47.7663183947111</v>
+        <v>63.39816107646547</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17.56789201070778</v>
+        <v>42.82527401129657</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6144041253481073</v>
+        <v>1.243624491664477</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-3.335383046183216</v>
+        <v>0.737496517129532</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6270</v>
+        <v>6277</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>667.4362449166448</v>
+        <v>678.9126877079127</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>34.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>63.39816105523928</v>
+        <v>49.29561307116624</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>42.82527400223323</v>
+        <v>42.07064271956436</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.243624491664477</v>
+        <v>0.3912687707912746</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.7374965173012455</v>
+        <v>-0.7319183994377876</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6405</v>
+        <v>6213</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>658.8255060195161</v>
+        <v>671.1440412534811</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.3</v>
+        <v>252.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.4136554258016</v>
+        <v>47.76631840680432</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>44.88618363896677</v>
+        <v>17.5678921132905</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.382550601951612</v>
+        <v>0.6144041253481073</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.625818730635056</v>
+        <v>-3.33538304652665</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6417</v>
+        <v>6210</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>645.0606802573158</v>
+        <v>649.3235598732942</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>133</v>
+        <v>20.85</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.20582559239092</v>
+        <v>49.33613176563992</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.6257004276479</v>
+        <v>21.25504703802524</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5060680257315795</v>
+        <v>1.432355987329429</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.784088730829218</v>
+        <v>-0.06572009870546031</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6207</v>
+        <v>6417</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>642.4605709489418</v>
+        <v>645.0606802573158</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>59.50471069341771</v>
+        <v>49.20582559925936</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>63.26864688229124</v>
+        <v>23.62570046342832</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7460570948941816</v>
+        <v>0.5060680257315795</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.9829245065301748</v>
+        <v>-1.784088731000931</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6274</v>
+        <v>6405</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>635.2818652826369</v>
+        <v>643.8255060195161</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1430</v>
+        <v>69.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.17681782343037</v>
+        <v>53.41365542993377</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>31.25200656079951</v>
+        <v>44.886183718681</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.528186528263684</v>
+        <v>2.382550601951612</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-40.89630657702102</v>
+        <v>-1.625818730654117</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6210</v>
+        <v>6207</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>634.3235598732942</v>
+        <v>642.4605709489418</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>20.85</v>
+        <v>124</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.33613171741863</v>
+        <v>59.5047106990857</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.2550467627686</v>
+        <v>63.26864700094963</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.432355987329429</v>
+        <v>0.7460570948941816</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.06572009863868269</v>
+        <v>-0.9829245067973034</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>612.9349800843639</v>
+        <v>639.090255894914</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>536</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.39931560339449</v>
+        <v>49.71800924822384</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>42.36035794827643</v>
+        <v>29.71863596140093</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7934980084363944</v>
+        <v>0.4090255894913951</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-2.241104271937194</v>
+        <v>-16.74407281732648</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6263</v>
+        <v>6274</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>606.2434894710215</v>
+        <v>635.2818652826369</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>158.5</v>
+        <v>1430</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.87711006453602</v>
+        <v>49.17681782592602</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>22.1363671551644</v>
+        <v>31.25200675983077</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6243489471021453</v>
+        <v>1.528186528263684</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-3.999639402914561</v>
+        <v>-40.89630657835636</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6290</v>
+        <v>6284</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>605.2437172164608</v>
+        <v>612.9349800843639</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>301.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.78183787635124</v>
+        <v>49.39931563404463</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.16583774037461</v>
+        <v>42.36035813610139</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5243717216460804</v>
+        <v>0.7934980084363944</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-7.372511609078099</v>
+        <v>-2.241104272662212</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6225</v>
+        <v>6263</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>590.8420916260466</v>
+        <v>606.2434894710215</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>23.3</v>
+        <v>158.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.50296537832135</v>
+        <v>44.87711010292007</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.45602669209626</v>
+        <v>22.13636722248699</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.08420916260465409</v>
+        <v>0.6243489471021453</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.414881451791915</v>
+        <v>-3.999639403773124</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6415</v>
+        <v>6290</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>580.5966382368697</v>
+        <v>605.2437172164608</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>487</v>
+        <v>301.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>44.70612182684034</v>
+        <v>47.7818378816639</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>31.98224873301237</v>
+        <v>22.16583783099537</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5596638236869712</v>
+        <v>0.5243717216460804</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-21.12067610976138</v>
+        <v>-7.372511609459668</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6451</v>
+        <v>6225</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>571.6782854394146</v>
+        <v>590.8420916260466</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>502</v>
+        <v>23.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.35618314675124</v>
+        <v>45.50296547141098</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>36.28335816073976</v>
+        <v>15.4560267969277</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6678285439414622</v>
+        <v>0.08420916260465409</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-19.88317950923028</v>
+        <v>-0.4148814520304058</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6285</v>
+        <v>6451</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>570.180494388386</v>
+        <v>571.6782854394146</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>270</v>
+        <v>502</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.70790903407893</v>
+        <v>44.35618315048021</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>30.85752076876623</v>
+        <v>36.28335830994219</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.018049438838595</v>
+        <v>0.6678285439414622</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-6.759452405355061</v>
+        <v>-19.88317951037505</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6184</v>
+        <v>6415</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>566.2119750290806</v>
+        <v>570.5966382368697</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>46.95</v>
+        <v>487</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>58.17277236417605</v>
+        <v>44.70612181718814</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.2566954160861</v>
+        <v>31.98224874930479</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6211975029080654</v>
+        <v>0.5596638236869712</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1078927186930734</v>
+        <v>-21.12067611052447</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6168</v>
+        <v>6184</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>565.0613781697566</v>
+        <v>566.2119750290806</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>26</v>
+        <v>46.95</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.42320378943265</v>
+        <v>58.17277242706187</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.00916316540409</v>
+        <v>22.2566954160861</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5061378169756675</v>
+        <v>0.6211975029080654</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.3826053004646295</v>
+        <v>0.1078927186739938</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6464</v>
+        <v>6168</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>562.7741846013446</v>
+        <v>565.0613781697566</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>60.85130909436173</v>
+        <v>48.42320378180332</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.82485252835232</v>
+        <v>17.00916323429466</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7774184601344641</v>
+        <v>0.5061378169756675</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0532321201463946</v>
+        <v>-0.3826053005027885</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6283</v>
+        <v>6464</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>553.066579159291</v>
+        <v>562.7741846013446</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>23.8</v>
+        <v>78</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.88482621941985</v>
+        <v>60.85130990485043</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.82169176736547</v>
+        <v>14.82485260273263</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8066579159291006</v>
+        <v>0.7774184601344641</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.2201304681237086</v>
+        <v>-0.0532321203944174</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6485</v>
+        <v>6285</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>551.9300440140247</v>
+        <v>555.180494388386</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>41.97739000459991</v>
+        <v>46.70790904978977</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25.91906977680306</v>
+        <v>30.85752081383877</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1930044014024711</v>
+        <v>1.018049438838595</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-3.87953587767782</v>
+        <v>-6.759452405832095</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6245</v>
+        <v>6283</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>551.7592121598755</v>
+        <v>553.066579159291</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>81</v>
+        <v>23.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.27851729097797</v>
+        <v>46.88482624135911</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.83680080543329</v>
+        <v>20.82169181575377</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6759212159875384</v>
+        <v>0.8066579159291006</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.134627842451211</v>
+        <v>-0.2201304682095642</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6224</v>
+        <v>6485</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>544.7373101338883</v>
+        <v>551.9300440140247</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>76.3</v>
+        <v>88</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.07735112721742</v>
+        <v>41.9773900159644</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30.9777551169783</v>
+        <v>25.91906982455598</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.473731013388834</v>
+        <v>0.1930044014024711</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.881155217610366</v>
+        <v>-3.879535877964024</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6216</v>
+        <v>6245</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>537.8375705626222</v>
+        <v>551.7592121598755</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>22.7</v>
+        <v>81</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.25463914479612</v>
+        <v>42.27851739529724</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.01459826276093</v>
+        <v>24.83680093107458</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.783757056262219</v>
+        <v>0.6759212159875384</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,11 +3909,11 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0395052243765747</v>
+        <v>-1.134627843080835</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>533.9360417531622</v>
+        <v>548.9360417531622</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>390.5</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.47574992573882</v>
+        <v>53.47575005138863</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.42875375230972</v>
+        <v>21.42875379232713</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.3936041753162143</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>6.167013002968913</v>
+        <v>6.167012998389888</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3972,41 +3972,41 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6288</v>
+        <v>6228</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>526.8310325240927</v>
+        <v>540.5976351321096</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>20.95</v>
+        <v>21.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.20701232738176</v>
+        <v>50.78990383463808</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23.25831693858013</v>
+        <v>2.602696332423994</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>0.0597635132109604</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0424721831038517</v>
+        <v>0.0814245594494184</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6228</v>
+        <v>6216</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>525.5976351321096</v>
+        <v>537.8375705626222</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.78990387697337</v>
+        <v>44.25463923753107</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2.602696408160458</v>
+        <v>23.01459828050237</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.0597635132109604</v>
+        <v>1.783757056262219</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0814245601458173</v>
+        <v>0.0395052242239379</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6237</v>
+        <v>6224</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>522.1269552665182</v>
+        <v>534.7373101338883</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>44.25</v>
+        <v>76.3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.70721770152553</v>
+        <v>48.07735113681436</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>32.23045431606671</v>
+        <v>30.9777551842473</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2126955266518184</v>
+        <v>0.473731013388834</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,51 +4121,51 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-1.378027062578777</v>
+        <v>-1.881155217772547</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6412</v>
+        <v>6288</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>520.9313649433186</v>
+        <v>526.8310325240927</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.7</v>
+        <v>20.95</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.68470694741001</v>
+        <v>51.54557993497567</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.62802577494336</v>
+        <v>23.83472184720588</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5931364943318577</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.965559882569257</v>
+        <v>0.0409797149548102</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6206</v>
+        <v>6237</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>504.8847620478426</v>
+        <v>522.1269552665182</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>131</v>
+        <v>44.25</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.47372937</v>
+        <v>43.70721773065521</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28.93301109656273</v>
+        <v>32.23045451967891</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.48847620478426</v>
+        <v>0.2126955266518184</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.164953121180359</v>
+        <v>-1.378027062884053</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6164</v>
+        <v>6412</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>495.4774938730781</v>
+        <v>520.9313649433186</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>12.8</v>
+        <v>91.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>53.57734443925095</v>
+        <v>46.68470696636784</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.16564569590802</v>
+        <v>29.62802573834845</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.047749387307804</v>
+        <v>0.5931364943318577</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0114082338299303</v>
+        <v>-1.965559883237036</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6198</v>
+        <v>6164</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>489.6132423869392</v>
+        <v>505.4774938730781</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>20.8</v>
+        <v>12.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.45881027989944</v>
+        <v>53.57734448055523</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9.621924222119979</v>
+        <v>17.16564582765987</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4613242386939237</v>
+        <v>1.047749387307804</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>1</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.340582882141012</v>
+        <v>-0.0114082338967087</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6217</v>
+        <v>6206</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>469.4606809339559</v>
+        <v>494.8847620478426</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.78647418983852</v>
+        <v>48.47372938779851</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.53299202306572</v>
+        <v>28.9330112500643</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9460680933955932</v>
+        <v>0.48847620478426</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-7.398087650885851</v>
+        <v>-2.164953121943539</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6235</v>
+        <v>6198</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>462.7252842248043</v>
+        <v>489.6132423869392</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>40.95</v>
+        <v>20.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>42.98636752686865</v>
+        <v>51.45881067772793</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.09771071722318</v>
+        <v>9.621924222119979</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2725284224804332</v>
+        <v>0.4613242386939237</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>1</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2252988312299902</v>
+        <v>0.340582882141012</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6416</v>
+        <v>6217</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>453.6328319341999</v>
+        <v>469.4606809339559</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>83</v>
+        <v>239</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.25936256443078</v>
+        <v>43.78647419150094</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>29.57194988875877</v>
+        <v>15.53299204142137</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3632831934199873</v>
+        <v>0.9460680933955932</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-1.229761457242655</v>
+        <v>-7.398087650943067</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6272</v>
+        <v>6235</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>451.4724814641678</v>
+        <v>462.7252842248043</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>35.25</v>
+        <v>40.95</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.54790282009872</v>
+        <v>42.98636760181886</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>32.36134447777911</v>
+        <v>22.09771078395876</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.647248146416782</v>
+        <v>0.2725284224804332</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1311395181820438</v>
+        <v>-0.225298831630653</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6474</v>
+        <v>6416</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>445.1990954021312</v>
+        <v>453.6328319341999</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>38.1</v>
+        <v>83</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.55172832786693</v>
+        <v>42.25936260756787</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.65999724775111</v>
+        <v>29.57194996387707</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.519909540213123</v>
+        <v>0.3632831934199873</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0695180785846105</v>
+        <v>-1.229761457853207</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6426</v>
+        <v>6272</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>440.3961734904414</v>
+        <v>451.4724814641678</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>193.5</v>
+        <v>35.25</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>35.45698801679085</v>
+        <v>51.54790290635722</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>22.13057117247952</v>
+        <v>32.36134453403891</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5396173490441427</v>
+        <v>0.647248146416782</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-9.642877733040391</v>
+        <v>-0.1311395185731689</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6222</v>
+        <v>6474</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>420.6411736310786</v>
+        <v>445.1990954021312</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>20.75</v>
+        <v>38.1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.837284110826</v>
+        <v>51.55172832786693</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>27.13936816769796</v>
+        <v>18.65999718929399</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.06411736310785569</v>
+        <v>0.519909540213123</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0164909846432705</v>
+        <v>-0.0695180785846105</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6230</v>
+        <v>6426</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>418.6881373120372</v>
+        <v>430.3961734904414</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>133</v>
+        <v>193.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>41.23148836308065</v>
+        <v>35.45698801228221</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.11640330088053</v>
+        <v>22.13057104707848</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3688137312037192</v>
+        <v>0.5396173490441427</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1029029477041314</v>
+        <v>-9.642877732887776</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6438</v>
+        <v>6222</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>418.586753054857</v>
+        <v>420.6411736310786</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>149.5</v>
+        <v>20.75</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>35.87946594921526</v>
+        <v>48.83728885873455</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.75500216561172</v>
+        <v>27.13936816769796</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3586753054857078</v>
+        <v>0.06411736310785569</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-2.202606422731179</v>
+        <v>-0.0164909846432705</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6215</v>
+        <v>6230</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>417.4385164720172</v>
+        <v>418.6881373120372</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.90827259501605</v>
+        <v>41.23148850617653</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.61690753297344</v>
+        <v>14.11640349998965</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.243851647201721</v>
+        <v>0.3688137312037192</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.734353000271297</v>
+        <v>-0.1029029491350952</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6183</v>
+        <v>6438</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>414.2237463018403</v>
+        <v>418.586753054857</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>89.7</v>
+        <v>149.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.89554949349788</v>
+        <v>35.87946602082513</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.59945994072807</v>
+        <v>24.75500235463777</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4223746301840251</v>
+        <v>0.3586753054857078</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1441599099286739</v>
+        <v>-2.202606425020697</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6234</v>
+        <v>6215</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>409.2534206936805</v>
+        <v>417.4385164720172</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>43.1</v>
+        <v>107</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.23085999656433</v>
+        <v>38.9082726366575</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21.60670958795873</v>
+        <v>20.6169075583764</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4253420693680548</v>
+        <v>0.243851647201721</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.077810929890279</v>
+        <v>-2.734353001282509</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6187</v>
+        <v>6183</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>396.5247136762774</v>
+        <v>414.2237463018403</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1085</v>
+        <v>89.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.69958780343895</v>
+        <v>39.89554961209328</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.61115411786098</v>
+        <v>22.59946009662806</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6524713676277446</v>
+        <v>0.4223746301840251</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-8.939304813172964</v>
+        <v>-0.1441599101576274</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6191</v>
+        <v>6187</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>379.2158515072746</v>
+        <v>411.5247136762774</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>93.8</v>
+        <v>1085</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45.20650704434916</v>
+        <v>48.69958781427585</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.72576432557996</v>
+        <v>13.61115437256173</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4215851507274646</v>
+        <v>0.6524713676277446</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.3155748284779993</v>
+        <v>-8.939304816702771</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6281</v>
+        <v>6234</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>354.7712728588841</v>
+        <v>409.2534206936805</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>51.6</v>
+        <v>43.1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.207468360392</v>
+        <v>42.23086001410218</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.78499488671778</v>
+        <v>21.60670976437233</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4771272858884073</v>
+        <v>0.4253420693680548</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1708409208708945</v>
+        <v>-1.077810930100155</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6470</v>
+        <v>6191</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>346.9930449151653</v>
+        <v>379.2158515072746</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>48.35</v>
+        <v>93.8</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.51033827492925</v>
+        <v>45.20650710898001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.21678505669593</v>
+        <v>12.72576442909315</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.699304491516536</v>
+        <v>0.4215851507274646</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0641416984387672</v>
+        <v>-0.3155748289168349</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6462</v>
+        <v>6281</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>337.7300450643979</v>
+        <v>354.7712728588841</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>110.5</v>
+        <v>51.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>38.38507240868029</v>
+        <v>52.20746843628493</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>24.50110237704394</v>
+        <v>15.78499479947101</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.2730045064397852</v>
+        <v>0.4771272858884073</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-2.719464413758313</v>
+        <v>0.1708409206419447</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6229</v>
+        <v>6470</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>332.0233480380198</v>
+        <v>346.9930449151653</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>26.35</v>
+        <v>48.35</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.49049056317247</v>
+        <v>48.51033837813287</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.44879807035834</v>
+        <v>15.21678514666986</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7023348038019781</v>
+        <v>0.699304491516536</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1838206303613881</v>
+        <v>-0.0641416986963424</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6275</v>
+        <v>6462</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>323.0251480161708</v>
+        <v>337.7300450643979</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>47.4</v>
+        <v>110.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.3493356804431</v>
+        <v>38.38507239959856</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>19.87605732699354</v>
+        <v>24.50110247376588</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3025148016170791</v>
+        <v>0.2730045064397852</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2500271251133194</v>
+        <v>-2.719464414158977</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6261</v>
+        <v>6229</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>321.5135562002758</v>
+        <v>332.0233480380198</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>97.3</v>
+        <v>26.35</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.96415785104756</v>
+        <v>48.4904906615487</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.94276664949376</v>
+        <v>16.44879817150086</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6513556200275807</v>
+        <v>0.7023348038019781</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-3.274080888823705</v>
+        <v>-0.1838206306189608</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6477</v>
+        <v>6275</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>311.4355728283922</v>
+        <v>323.0251480161708</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>33.5</v>
+        <v>47.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.6072707220194</v>
+        <v>42.34933572869691</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.54400861465205</v>
+        <v>19.87605744567292</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.643557282839217</v>
+        <v>0.3025148016170791</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0552534069619756</v>
+        <v>-0.2500271253708934</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6226</v>
+        <v>6456</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>311.3883570826965</v>
+        <v>322.3053173958407</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>12.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.13115054402923</v>
+        <v>46.05788803745701</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.35029041000144</v>
+        <v>16.81887442197359</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6388357082696449</v>
+        <v>0.2305317395840733</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1691111346463696</v>
+        <v>-1.466908658137235</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6456</v>
+        <v>6261</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>307.3053173958407</v>
+        <v>321.5135562002758</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.0578880356571</v>
+        <v>39.96415783300512</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.81887442121687</v>
+        <v>22.9427666958305</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2305317395840733</v>
+        <v>0.6513556200275807</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.466908658079995</v>
+        <v>-3.274080888880927</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6201</v>
+        <v>6477</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>298.0108021144565</v>
+        <v>311.4355728283922</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>47.2</v>
+        <v>33.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.89707908068762</v>
+        <v>48.60727095613174</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>24.24515302374684</v>
+        <v>15.54400876659945</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3010802114456447</v>
+        <v>2.643557282839217</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>2</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0716136692155796</v>
+        <v>-0.0552534071527703</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6418</v>
+        <v>6226</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>293.7571803520551</v>
+        <v>311.3883570826965</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>32</v>
+        <v>12.1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>52.13690932367798</v>
+        <v>43.13115056279825</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23.32619439279163</v>
+        <v>17.3502904020072</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8757180352055081</v>
+        <v>0.6388357082696449</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1225518440864628</v>
+        <v>-0.1691111346711729</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6194</v>
+        <v>6201</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>292.578638754186</v>
+        <v>298.0108021144565</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>32.55</v>
+        <v>47.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>43.78055826332135</v>
+        <v>38.89707912443998</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.52990571552866</v>
+        <v>24.24515310670145</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2578638754185993</v>
+        <v>0.3010802114456447</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2357700000347006</v>
+        <v>-0.07161366948269279</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6423</v>
+        <v>6418</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>283.7032263474908</v>
+        <v>293.7571803520551</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>32</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>29.09211059093741</v>
+        <v>52.13690931773412</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>24.41672149727599</v>
+        <v>23.32619448322079</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8703226347490852</v>
+        <v>0.8757180352055081</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.66234936237589</v>
+        <v>0.1225518440387633</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6185</v>
+        <v>6194</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>276.2190263629022</v>
+        <v>292.578638754186</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14</v>
+        <v>32.55</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>48.11869611051023</v>
+        <v>43.78055831227005</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.50854551751329</v>
+        <v>20.52990575337181</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.621902636290223</v>
+        <v>0.2578638754185993</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0065867098019583</v>
+        <v>-0.2357700001491755</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6192</v>
+        <v>6423</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>273.6917026295268</v>
+        <v>283.7032263474908</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>117.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.97850922276105</v>
+        <v>29.09211043426889</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.05955178123152</v>
+        <v>24.41672149450003</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8691702629526841</v>
+        <v>0.8703226347490852</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.476514797993327</v>
+        <v>-1.662349361345592</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6246</v>
+        <v>6185</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>272.871230397225</v>
+        <v>276.2190263629022</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15.35</v>
+        <v>14</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.95074590006645</v>
+        <v>48.1186962007204</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.14517746544609</v>
+        <v>16.5085455674549</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7871230397225001</v>
+        <v>1.621902636290223</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0187946683925832</v>
+        <v>-0.0065867099355149</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6167</v>
+        <v>6192</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>269.5446843400171</v>
+        <v>273.6917026295268</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>11.6</v>
+        <v>117.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.87258749201862</v>
+        <v>36.97850926096282</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.84916358550448</v>
+        <v>23.05955198252743</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4544684340017086</v>
+        <v>0.8691702629526841</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.009961695396764701</v>
+        <v>-1.476514798546636</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6233</v>
+        <v>6246</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>256.9244143737302</v>
+        <v>272.871230397225</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>23.5</v>
+        <v>15.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.09521665235705</v>
+        <v>45.95074586036513</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.5229876462298</v>
+        <v>16.1451775718851</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6924414373730167</v>
+        <v>0.7871230397225001</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1999832455341171</v>
+        <v>-0.0187946683639632</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6176</v>
+        <v>6167</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>246.8955762334722</v>
+        <v>269.5446843400171</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>91.3</v>
+        <v>11.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.56075713362758</v>
+        <v>44.8725875554119</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>29.49032607466522</v>
+        <v>16.8491636536114</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6895576233472144</v>
+        <v>0.4544684340017086</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.689327607520469</v>
+        <v>-0.0099616954948618</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6203</v>
+        <v>6233</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>211.1862217439997</v>
+        <v>256.9244143737302</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>23.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.45873256720958</v>
+        <v>39.09521668093807</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>23.37311976603001</v>
+        <v>14.52298784545416</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6186221743999711</v>
+        <v>0.6924414373730167</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.6783927050326707</v>
+        <v>-0.1999832456390522</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6188</v>
+        <v>6176</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>204.9718493268477</v>
+        <v>246.8955762334722</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>81.2</v>
+        <v>91.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.86559010721904</v>
+        <v>35.56075715060396</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.3631398827459</v>
+        <v>29.49032604863315</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4971849326847719</v>
+        <v>0.6895576233472144</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.4992372119382178</v>
+        <v>-1.689327608188252</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6441</v>
+        <v>6203</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>191.5636291063111</v>
+        <v>211.1862217439997</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>23.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.51020419769213</v>
+        <v>40.45873264675801</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.79656221354166</v>
+        <v>23.37311988285946</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1563629106311094</v>
+        <v>0.6186221743999711</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1866604187693174</v>
+        <v>-0.6783927056241554</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6266</v>
+        <v>6188</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>184.8198149429533</v>
+        <v>204.9718493268477</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>25.45</v>
+        <v>81.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>29.08393131908009</v>
+        <v>44.86559012503205</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.12717461852144</v>
+        <v>12.36314002637804</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9819814942953284</v>
+        <v>0.4971849326847719</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.225603812665763</v>
+        <v>-0.499237212453361</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6218</v>
+        <v>6441</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>182.3642194641695</v>
+        <v>191.5636291063111</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>31.8</v>
+        <v>23.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>35.64142415990119</v>
+        <v>45.51020420531521</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.67393634130522</v>
+        <v>14.79656225334266</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2364219464169485</v>
+        <v>0.1563629106311094</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,48 +6347,48 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.067174283263981</v>
+        <v>-0.1866604189791897</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6287</v>
+        <v>6266</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>168.8193640139415</v>
+        <v>184.8198149429533</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>25.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G112" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.36725836105252</v>
+        <v>29.08393136054276</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0.9513778337062641</v>
+        <v>21.12717474210172</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.9819814942953284</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,51 +6400,51 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0065724218287724</v>
+        <v>-0.2256038127420821</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6243</v>
+        <v>6287</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>164.5096389978013</v>
+        <v>183.8193640139415</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>30.95</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G113" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>41.44746733512341</v>
+        <v>51.36725836105252</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>26.40745853964019</v>
+        <v>0.9687777134870372</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4509638997801333</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.4871459349018032</v>
+        <v>-0.0065724218287724</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6236</v>
+        <v>6218</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>105</v>
+        <v>182.3642194641695</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.02625827096713</v>
+        <v>35.64142418679172</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.565112674595058</v>
+        <v>14.67393646363458</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0</v>
+        <v>0.2364219464169485</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,62 +6506,168 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0349354445040628</v>
+        <v>-1.067174283464315</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>6243</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>迅杰</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>164.5096389978013</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>41.44746734020165</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>26.40745861851237</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4509638997801333</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.4871459350353618</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>48.02625827096713</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>9.565112674595058</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0349354445040628</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>6276</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>安鈦克</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>67.47140504695358</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>32.94391801377165</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>19.14544900215686</v>
-      </c>
-      <c r="J115" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>32.94391819311207</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>19.14544900560948</v>
+      </c>
+      <c r="J117" s="2" t="n">
         <v>0.747140504695358</v>
       </c>
-      <c r="K115" s="2" t="n">
+      <c r="K117" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-0.1564428001965625</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.1564428005781502</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
